--- a/results/direct_inference/mgsm/tiny-aya-global/summary_majority.xlsx
+++ b/results/direct_inference/mgsm/tiny-aya-global/summary_majority.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="all_parse_failures" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,18 +461,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
         <v>250</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -486,14 +487,14 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
         <v>250</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -512,14 +513,14 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
         <v>250</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -538,14 +539,14 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
         <v>250</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -564,18 +565,116 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
         <v>250</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>lang</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>q_idx</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>expected</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>raw_response</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>78</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">যদি রেমন্ড সারার তুলনায় অর্ধেক লন্ড্রি করে, এবং সারা ডেভিডের তুলনায় 4 গুণ বেশি লন্ড্রি করে, তবে যদি </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>প্রশ্নটি সঠিকভাবে সমাধান করা যায় না, কারণ প্রদত্ত তথ্যে রেমন্ড ও ডেভিডের লন্ড্রির পরিমাণ সম্পর্কে কোনো তথ্য নেই। তাই, তাদের লন্ড্রির পরিমাণের পার্থক্যের হিসাব করা সম্ভব নয়।</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>171</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>মার্চিং ব্যান্ড নতুন ইউনিফর্মের অর্ডার করেছে। প্রতিটি ইউনিফর্মের সাথে একটি করে টুপি আছে যার দাম $25,</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>150</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>প্রশ্নে প্যান্টের দাম উল্লেখ নেই, তাই মোট দাম গণনা করা সম্ভব নয়। উত্তর: **অজানা**</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/results/direct_inference/mgsm/tiny-aya-global/summary_majority.xlsx
+++ b/results/direct_inference/mgsm/tiny-aya-global/summary_majority.xlsx
@@ -461,18 +461,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
         <v>250</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -487,14 +487,14 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>250</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -513,14 +513,14 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>250</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -539,18 +539,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>250</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -565,18 +565,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>250</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,52 +628,182 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bn</t>
+          <t>sw</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">যদি রেমন্ড সারার তুলনায় অর্ধেক লন্ড্রি করে, এবং সারা ডেভিডের তুলনায় 4 গুণ বেশি লন্ড্রি করে, তবে যদি </t>
+          <t>Griffin alikuwa na chipsi 24, lakini Kyle alichukua 5. Billy alichukua mara mbili zaidi ya Kyle. Gin</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>প্রশ্নটি সঠিকভাবে সমাধান করা যায় না, কারণ প্রদত্ত তথ্যে রেমন্ড ও ডেভিডের লন্ড্রির পরিমাণ সম্পর্কে কোনো তথ্য নেই। তাই, তাদের লন্ড্রির পরিমাণের পার্থক্যের হিসাব করা সম্ভব নয়।</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bn</t>
+          <t>sw</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>171</v>
+        <v>245</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>মার্চিং ব্যান্ড নতুন ইউনিফর্মের অর্ডার করেছে। প্রতিটি ইউনিফর্মের সাথে একটি করে টুপি আছে যার দাম $25,</t>
+          <t>Griffin alikuwa na chipsi 24, lakini Kyle alichukua 5. Billy alichukua mara mbili zaidi ya Kyle. Gin</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>প্রশ্নে প্যান্টের দাম উল্লেখ নেই, তাই মোট দাম গণনা করা সম্ভব নয়। উত্তর: **অজানা**</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>245</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Griffin alikuwa na chipsi 24, lakini Kyle alichukua 5. Billy alichukua mara mbili zaidi ya Kyle. Gin</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>te</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>టౌలా ఒక బేకరీకి వెళ్లి, వివిధ రకాలైన పేస్ట్రీలను కొనుగోలు చేసింది. ఆమె డజను $68 ఖరీదుతో 3 డజన్ల డోనట</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>694</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>$ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>te</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>టౌలా ఒక బేకరీకి వెళ్లి, వివిధ రకాలైన పేస్ట్రీలను కొనుగోలు చేసింది. ఆమె డజను $68 ఖరీదుతో 3 డజన్ల డోనట</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>694</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>$ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>te</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>75</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ఆర్టీకి రైతు మార్కెట్ వద్ద పువ్వుల స్టాండ్ ఉంది. అతడు మూడు రకాలైన పువ్వులు అమ్ముతాడు: బంతిపూలు, పెటూ</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>88</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>$ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>te</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>75</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ఆర్టీకి రైతు మార్కెట్ వద్ద పువ్వుల స్టాండ్ ఉంది. అతడు మూడు రకాలైన పువ్వులు అమ్ముతాడు: బంతిపూలు, పెటూ</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>88</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>$ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $ $</t>
         </is>
       </c>
     </row>
